--- a/p3_data_preparation/data/germany/integrate_data/df_teams.xlsx
+++ b/p3_data_preparation/data/germany/integrate_data/df_teams.xlsx
@@ -443,60 +443,60 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>heidenheim</t>
+          <t>augsburg</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>eintracht frankfurt</t>
+          <t>dortmund</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>union berlin</t>
+          <t>eintracht frankfurt</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fc koln</t>
+          <t>bayern munich</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>dortmund</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
     </row>
@@ -515,144 +515,144 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>union berlin</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>wolfsburg</t>
+          <t>werder bremen</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hoffenheim</t>
+          <t>bayer leverkusen</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>S0hPB9rA</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>darmstadt</t>
+          <t>bochum</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>mainz</t>
+          <t>freiburg</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>b  monchengladbach</t>
+          <t>rb leipzig</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>S0hPB9rA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>bayer leverkusen</t>
+          <t>darmstadt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>augsburg</t>
+          <t>heidenheim</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bayern munich</t>
+          <t>hoffenheim</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>freiburg</t>
+          <t>mainz</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>rb leipzig</t>
+          <t>wolfsburg</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>bochum</t>
+          <t>fc koln</t>
         </is>
       </c>
     </row>
